--- a/daily_matches/job_matches_2026-05-20.xlsx
+++ b/daily_matches/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
+          <t>Data Engineer, Marketing Data Operations</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB, NoSQL</t>
+          <t>Data Scientist, RAG, S3, EC2, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
+          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Redshift, Kinesis, Jenkins, Git, Redshift, MySQL, NoSQL, Python</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, BigQuery, Dataflow, Docker, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0504cd8c91e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=6725bf29a07dcb85</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Advanced AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce4b719e0013ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer (Generative AI)</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, CI/CD, Git, Snowflake, BigQuery, Hadoop, Python, SQL</t>
+          <t>RAG, Copilot, S3, Kinesis, Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6066bc70296362</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Sr Applied AI Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Glue, Docker, Kubernetes, CI/CD, Terraform, Git, MongoDB, NoSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Git, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5ba2a07350dfe3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Applied AI Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sciata</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, FastAPI, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Git, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ca12a0314b40b3</t>
+          <t>https://www.indeed.com/viewjob?jk=354cb0de310de41e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Applied AI Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Git, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b89204147a7518b3</t>
+          <t>https://www.indeed.com/viewjob?jk=76e261f79f911ace</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr Applied AI Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>True Classic</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Git, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8363f0871e4f4b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f2733534d38d77</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Infra Engineer Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>True Classic</t>
+          <t>Meshy LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, S3, Data Lake, FastAPI, Kubernetes, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b9b1967b3474b2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf18d8c4970e9797</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>True Classic</t>
+          <t>Newity LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>S3, Glue, Redshift, BigQuery, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28aa98cfeb2e669</t>
+          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Agentic Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>True Classic</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, FAISS, Pinecone, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=275f102e5daa6602</t>
+          <t>https://www.indeed.com/viewjob?jk=d6b761ec22282223</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c53274a80c0bed</t>
+          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GEN AI Engineer (Specialist - Research Engineering)</t>
+          <t>Senior Software Engineer (Backend) - Ai Platform Team</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Java, Hypothesis Testing</t>
+          <t>RAG, PyTorch, S3, Data Lake, Kafka, MySQL, Cassandra, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=041f92ae4b14605b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3f5a69dfd27ec9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Senior Software Engineer (Backend) - Ai Platform Team</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AssetWorks</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, PyTorch, S3, Data Lake, Kafka, MySQL, Cassandra, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=107ec4980e2fa657</t>
+          <t>https://www.indeed.com/viewjob?jk=3220d3a3cadc7277</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Senior Software Engineer (Backend) - Ai Platform Team</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AssetWorks</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, PyTorch, S3, Data Lake, Kafka, MySQL, Cassandra, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aa2aae6a16e95a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e0a1223daa0d6d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-Stack Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Social Impact</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Jenkins, GitHub Actions, Git, PySpark, Hadoop, SQL, R, Scala</t>
+          <t>FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. QA Engineer</t>
+          <t>Database Engineer / Database Administrator</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agero</t>
+          <t>FinQuery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, XGBoost, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Copilot, Jenkins, GitHub Actions, Terraform, Git, Snowflake, PostgreSQL, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66500aeb2eba13d5</t>
+          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026 Associate Data Engineer</t>
+          <t>(USA) Data Scientist III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eversource Energy</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Windsor, CT, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, PostgreSQL, MySQL, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, Git, PySpark, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9ac0c78377cc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=9915be41b8af888b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Retrieval &amp; Relevance Engineer (RAG / Hybrid Search)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>iBusiness Funding</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Git, Snowflake, MongoDB, Python, SQL, R, Scala</t>
+          <t>RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc46dd3a10c782c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Software Engineering PMTS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Terraform, Git, Kafka, R, Java</t>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,42 +1161,1442 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2995d1c2ff6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=03005ed057172d17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SR Automation Engineer</t>
+          <t>Software Engineering PMTS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=055429ab8bf62c8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Product Security Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, FastAPI, Kubernetes, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbb2e9078277b2d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist - Substation Engineering (Utilities)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ComEd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Oakbrook Terrace, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Hadoop, Dask, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3ba9f12ab7fed88</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Versant Health</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Synapse, Data Lake, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0edb37d37da2eeb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Versant Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Troy, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Synapse, Data Lake, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d38387b09c76d545</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Safal Partners</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Prompt Engineering, FastAPI, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ead9c6972e80ab89</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Releady</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Agentic Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47864e1c6cd3ef19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test - AI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Delos Data</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46e3f8d6a4f9e6cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83bb589c84ea1985</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=035704d257f1a600</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dad7abdd0b2952f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=832ae5e89caf2c77</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ecbbaa89bc203e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01f238c83a644994</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f90dbf82d2cb24f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9fb17a9a3fad1a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd9156c6c8d0da45</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab6d7428b70f4d7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e58869e62c88d3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>San Francisco, CA, US USA</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48178d2fae2184ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a73f91741785458a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2317c7aec45cc19</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=511d1201e4f1c1ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c413a896f9235af3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7500664650f34c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a3a47acd276be06</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Signup &amp; Activation)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb4b2c490a4b0820</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BISSELL</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Glue, Redshift, Data Lake, CI/CD, Redshift, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e869ac1713588267</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FLEX Sr. Systems Engineer - Observability</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Marriott International</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Kubernetes, Terraform, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3edc1f038d9d885</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Applied AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, S3, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d61e7764d07e8c2</t>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db277c78e529d63f</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Applied AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dc6b5722a46f0f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Applied AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb881d1e73ada22b</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Applied AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c012dfcdd9468862</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Operations Analyst (Data Scientist)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>World Bank Group</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ade42985c4db6fdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data Engineer IV – AI &amp; Data Products</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Upbound Group</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Copilot, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d4b70f1e8b3bd52</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer- Full Stack</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Newport Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a994a89b20db12c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SOFTWARE DEVELOPMENT ENGINEER- PROCESS AUTOMATION &amp; AI</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Yokogawa</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sugar Land, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52383768d361816f</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6ecb564882248e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Drupal Architect</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NuAxis Innovations</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>FastAPI, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f2f560f230e6591</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AI Innovation Analyst - Internal</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kaseya</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Prompt Engineering, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50c4a8cbf5b25d89</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-20.xlsx
+++ b/daily_matches/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Automation AI Engineer</t>
+          <t>Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, CI/CD, Git, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c25ba52f21681f5</t>
+          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=198b17d882618b2f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, Energy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Tableau</t>
+          <t>Generative AI, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed396163c7720de0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Forward Deployed Engineer (Foundry)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trinity Industries</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, CI/CD, Snowflake, Databricks, PySpark, Tableau, Python, SQL</t>
+          <t>RAG, AWS SageMaker, EC2, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e98784d3b069887</t>
+          <t>https://www.indeed.com/viewjob?jk=cafa1674464c020f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Strategic Intelligence &amp; Advanced Analytics Engineer</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UT Southwestern Medical Center</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Matplotlib, Python</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8942bbfda3594c99</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2850e7510faaa4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SRE / DevOps Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>Generative AI, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
+          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Engineering Associate - Digital Platform Performance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, Hugging Face, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac09e9496c1cf07</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f6c6357d4eee69</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Data Engineer (Telecommunications)</t>
+          <t>Engineering Associate - Digital Platform Performance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R, Optimization</t>
+          <t>Generative AI, LangChain, Hugging Face, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de513efb38e72c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4775c9b96d7374ee</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mem0</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, EC2, FastAPI, Docker, Kubernetes, Kafka, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d505be2a439d27</t>
+          <t>https://www.indeed.com/viewjob?jk=8e5e01e413843548</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quantitative Researcher</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>QuantCo</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, XGBoost, LightGBM, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, TensorFlow, PyTorch, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a2c72b6c0eb1f47</t>
+          <t>https://www.indeed.com/viewjob?jk=f121b8260088ae35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, EC2, AKS, CI/CD, Jenkins, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, TensorFlow, PyTorch, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
+          <t>https://www.indeed.com/viewjob?jk=d23cfb41778bb85b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Latitude AI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, EC2, AKS, CI/CD, Jenkins, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
+          <t>https://www.indeed.com/viewjob?jk=246050d89d6917c0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, EC2, AKS, CI/CD, Jenkins, R, Java, Scala, Optimization</t>
+          <t>RAG, Synapse, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Developer (Genomics Analysis Team)</t>
+          <t>Engineering Associate - Data Engineering &amp; Analytics</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lawrence Berkeley National Laboratory</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,122 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, CI/CD, Git, Matplotlib, Python, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, Kafka, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b6432656b648121</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Engineering Associate - Data Engineering &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Kafka, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c5a89e912f3aa68</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist Advisor</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Southern California Edison</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pomona, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acee9dca9005d063</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a7c419a67e2a3be</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Data Science</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gap Inc.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Tableau, Python, SQL, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb6578406c0c4a27</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-20.xlsx
+++ b/daily_matches/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Python Full Stack Developer</t>
+          <t>Senior Associate - AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, CI/CD, Git, PostgreSQL, MySQL, NoSQL</t>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, S3, EC2, Redshift, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
+          <t>https://www.indeed.com/viewjob?jk=9cc5523e609d6490</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost, MLflow, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198b17d882618b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, S3, Docker, Kubernetes, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7272314c6d38b5d8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI Agent Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>GenuineXs LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,69 +591,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, EC2, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cafa1674464c020f</t>
+          <t>https://www.indeed.com/viewjob?jk=567bf2a242dfe814</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Sr. Software Engineer, AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>NinjaTrader</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Athena, BigQuery, Terraform, BigQuery, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2850e7510faaa4</t>
+          <t>https://www.indeed.com/viewjob?jk=95dd7a9fee83dfeb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Humbly Confident Senior Laravel Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Chiro Cat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Python</t>
+          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
+          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineering Associate - Digital Platform Performance</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Hugging Face, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f6c6357d4eee69</t>
+          <t>https://www.indeed.com/viewjob?jk=23dcb256aacd41d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineering Associate - Digital Platform Performance</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Hugging Face, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4775c9b96d7374ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Sr. Software Engineer II, Fullstack - NT Connect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>NinjaTrader</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Terraform, Git, Kafka, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e5e01e413843548</t>
+          <t>https://www.indeed.com/viewjob?jk=5bae515d66724e0a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, TensorFlow, PyTorch, Kubernetes, Python, R, Java</t>
+          <t>RAG, Data Lake, CI/CD, Databricks, PySpark, MongoDB, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f121b8260088ae35</t>
+          <t>https://www.indeed.com/viewjob?jk=2f31e24ce7df1352</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Machine Learning Engineer III - FES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Fanatics Betting &amp; Gaming</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, TensorFlow, PyTorch, Kubernetes, Python, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, AWS SageMaker, Git, Databricks, Kafka, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23cfb41778bb85b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e71c55ab6b25777</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Full Stack Engineer - Remote -W2 Only</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Latitude AI</t>
+          <t>Digital iTechnology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=246050d89d6917c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Business Applications Analyst II- Fort Myers</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Millennium Physician Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Optimization</t>
+          <t>Generative AI, Cortex, TensorFlow, PyTorch, Athena, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b60272c9faa3a0b0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineering Associate - Data Engineering &amp; Analytics</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kafka, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6432656b648121</t>
+          <t>https://www.indeed.com/viewjob?jk=07441c6e23821f2a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineering Associate - Data Engineering &amp; Analytics</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kafka, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,77 +986,252 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5a89e912f3aa68</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5b76c27e503488</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Scientist Advisor</t>
+          <t>Senior AI Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southern California Edison</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, LangChain, RAG, Pinecone, CI/CD, Snowflake, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7c419a67e2a3be</t>
+          <t>https://www.indeed.com/viewjob?jk=1603008e641bd8e3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Science</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89d4f32f720c7b3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist I (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LexisNexis Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, XGBoost, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03c0b5032fe43367</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist I (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, XGBoost, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71fc6f94278de266</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Corporate Finance – Data Science Product Associate</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Newark, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Tableau, Python, SQL, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6578406c0c4a27</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f385a892ad48cda</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr Product Mgr</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Snowflake, Databricks, BigQuery, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f2b0e4b706a7459</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>United Educators</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95f3f2eedd16a5da</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-20.xlsx
+++ b/daily_matches/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Associate - AI Engineer</t>
+          <t>AI/ML Intern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Xpedient Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, S3, EC2, Redshift, Docker, Kubernetes, CI/CD</t>
+          <t>TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc5523e609d6490</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1d8e827779774e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost, MLflow, Git</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7272314c6d38b5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Agent Software Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GenuineXs LLC</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=567bf2a242dfe814</t>
+          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, AI</t>
+          <t>Data Scientist II - Client Analysis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NinjaTrader</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Athena, BigQuery, Terraform, BigQuery, Python</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95dd7a9fee83dfeb</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cf00c21318eb74</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Humbly Confident Senior Laravel Engineer</t>
+          <t>Data Scientist II - Client Analysis</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chiro Cat</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8ef0df9e0e31c5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Scientist II - Client Analysis</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, MLflow, Docker, Git</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23dcb256aacd41d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d3c90aa78be26e9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist II - Client Analysis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f68e10c56a9724</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, Fullstack - NT Connect</t>
+          <t>Data Scientist II - Client Analysis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NinjaTrader</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Terraform, Git, Kafka, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bae515d66724e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=872a68e9d110cb5b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Engineer, epocrates</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, PySpark, MongoDB, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, AWS SageMaker, Athena, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f31e24ce7df1352</t>
+          <t>https://www.indeed.com/viewjob?jk=724ca69b243d36df</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III - FES</t>
+          <t>Data Scientist | Forensic and Litigation Consulting</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fanatics Betting &amp; Gaming</t>
+          <t>FTI Consulting, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, AWS SageMaker, Git, Databricks, Kafka, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, spaCy, MLflow, FastAPI, Docker, Git, Databricks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e71c55ab6b25777</t>
+          <t>https://www.indeed.com/viewjob?jk=49130f05512506f6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Remote -W2 Only</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Digital iTechnology</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>Docker, Git, Kafka, PostgreSQL, Cassandra, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0db13ad0d412cf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT Business Applications Analyst II- Fort Myers</t>
+          <t>AI Engineer - Go To Market</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Millennium Physician Group</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Temple Terrace, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, Cortex, TensorFlow, PyTorch, Athena, Snowflake, Databricks, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, GCP Vertex AI, Docker, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60272c9faa3a0b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d43058112019f11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>CARVANA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07441c6e23821f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=f870aee987168a3a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Software Engineer, Internal Tools</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, S3, Athena, GitHub Actions, Git, Snowflake, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5b76c27e503488</t>
+          <t>https://www.indeed.com/viewjob?jk=e4cdab460153cd8c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Developer</t>
+          <t>Junior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>BrandRank.ai</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Pinecone, CI/CD, Snowflake, Databricks, Python, R, Scala</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1603008e641bd8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c344e045ac04bc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>AtkinsRéalis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d4f32f720c7b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a06544e7a5d5b36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Scientist I (Hybrid)</t>
+          <t>Senior SRE (Site Reliability Engineer)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, XGBoost, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c0b5032fe43367</t>
+          <t>https://www.indeed.com/viewjob?jk=00b2f164a079dde2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Scientist I (Hybrid)</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, XGBoost, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71fc6f94278de266</t>
+          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Corporate Finance – Data Science Product Associate</t>
+          <t>Senior AI/ML Applied Scientist - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Python, SQL, R, Scala, A/B Testing</t>
+          <t>Generative AI, Prompt Engineering, Azure ML, Git, Snowflake, Databricks, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f385a892ad48cda</t>
+          <t>https://www.indeed.com/viewjob?jk=4c6d2f3909909a18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Product Mgr</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PLACE Corporate Careers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, Snowflake, Databricks, BigQuery, SQL, R, Scala, A/B Testing</t>
+          <t>AI Engineer, RAG, Copilot, BigQuery, Snowflake, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2b0e4b706a7459</t>
+          <t>https://www.indeed.com/viewjob?jk=797b0ef6d680cad6</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>United Educators</t>
+          <t>Neara</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,157 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6f240758ece9ff7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Neara</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=311a85238cefcf56</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Neara</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15b6118e3b3e04f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Neara</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eef9e1996794f20e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>United Educators</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95f3f2eedd16a5da</t>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f80cb7119b82f7f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-20.xlsx
+++ b/daily_matches/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Intern</t>
+          <t>Senior Machine Learning Engineer (Temporary)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Xpedient Technologies</t>
+          <t>Brooks Running</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, BigQuery, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1d8e827779774e</t>
+          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>Generative AI, LangChain, RAG, FastAPI, Docker, CI/CD, Terraform, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
+          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
+          <t>https://www.indeed.com/viewjob?jk=af5096f99a1a0d06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>Generative AI, Data Lake, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist II - Client Analysis</t>
+          <t>Senior Software Engineer – Data Engineering (GCP &amp; AI) (contract)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Data Lake, Dataflow, Docker, Kubernetes, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,172 +636,172 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cf00c21318eb74</t>
+          <t>https://www.indeed.com/viewjob?jk=864bf732311fb751</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist II - Client Analysis</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
+          <t>RAG, S3, EC2, CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8ef0df9e0e31c5</t>
+          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist II - Client Analysis</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
+          <t>RAG, S3, EC2, CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d3c90aa78be26e9</t>
+          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist II - Client Analysis</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
+          <t>RAG, S3, EC2, CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f68e10c56a9724</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist II - Client Analysis</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
+          <t>RAG, S3, EC2, CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=872a68e9d110cb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer, epocrates</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Air Today USA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, AWS SageMaker, Athena, Git, Python</t>
+          <t>Copilot, FastAPI, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ca69b243d36df</t>
+          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist | Forensic and Litigation Consulting</t>
+          <t>Mid-level DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FTI Consulting, Inc.</t>
+          <t>Ella Wholesales Coffee</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, spaCy, MLflow, FastAPI, Docker, Git, Databricks</t>
+          <t>Copilot, FastAPI, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49130f05512506f6</t>
+          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>SAP iXp Intern - AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Docker, Git, Kafka, PostgreSQL, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, PyTorch, FastAPI, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0db13ad0d412cf</t>
+          <t>https://www.indeed.com/viewjob?jk=1a21dd997eea041c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer - Go To Market</t>
+          <t>Java developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Tech Genius</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Temple Terrace, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, GCP Vertex AI, Docker, CI/CD, Git, Python</t>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d43058112019f11</t>
+          <t>https://www.indeed.com/viewjob?jk=483447a16530d4f7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CARVANA</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f870aee987168a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer, Internal Tools</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VEVO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Athena, GitHub Actions, Git, Snowflake, PostgreSQL, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4cdab460153cd8c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f986b7667ce4b5f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer (SRE)</t>
+          <t>Sr Software Engineer, Build and Release Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BrandRank.ai</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c344e045ac04bc</t>
+          <t>https://www.indeed.com/viewjob?jk=fe77948a6745c2be</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Solution Owner | AI &amp; Data Solutions</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AtkinsRéalis</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, BigQuery, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a06544e7a5d5b36</t>
+          <t>https://www.indeed.com/viewjob?jk=9ac97a7be4ed2b2d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior SRE (Site Reliability Engineer)</t>
+          <t>Senior Solution Owner | AI &amp; Data Solutions</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, BigQuery, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00b2f164a079dde2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c105f428e749f6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Senior Solution Owner | AI &amp; Data Solutions</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, BigQuery, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=065dc9ad3b2548bb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI/ML Applied Scientist - Remote</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Azure ML, Git, Snowflake, Databricks, Python, R, Optimization</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c6d2f3909909a18</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d8f9a89cafe5ef</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PLACE Corporate Careers</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, BigQuery, Snowflake, BigQuery, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797b0ef6d680cad6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e84660f7e9cf19f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Internal GenAI engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Neara</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f240758ece9ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=9433727cb0c84069</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Internal GenAI engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Neara</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311a85238cefcf56</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2f8b936bd1939d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data/AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Neara</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b6118e3b3e04f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Neara</t>
+          <t>DynPro.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,42 +1336,742 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef9e1996794f20e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c75716e5bab170e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer II - Analytics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>United Educators</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15bd37695704d0b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Protiviti</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, PySpark, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>WellSky</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e633df748f67fb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Intern, Data Science</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LiveRamp</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, BigQuery, Git, BigQuery, PySpark, Hadoop, Matplotlib, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ebe7cc97cc98337</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Intern, Data Science</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LiveRamp</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, BigQuery, Git, BigQuery, PySpark, Hadoop, Matplotlib, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a87af80a4737a692</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Portfolio BI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, NoSQL, Tableau, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Analyst - Data Engineering 5A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e339014ef594f24c</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Protiviti</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, PySpark, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist, People &amp; Workforce Analytics</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ivy Rehab Network</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Data Lake, Snowflake, Power BI, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dce8a40632666565</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Los Altos, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>10</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Databricks, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f80cb7119b82f7f</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f019446e02ae7c21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bee3fb9d6869342d</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Landair Property Advisors</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Docker, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d938a48d568ba73b</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9ba3a5ca06cf6f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=367666b24fd9e060</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Software Engineer (Fullstack)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Clearstory</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, BigQuery, Docker, CI/CD, Git, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14a4f1d85ae4121a</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Babel Street</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00df9ee9735449cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Babel Street</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24db1692b03a715b</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer - NYC / Dallas / Los Angeles</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Portfolio BI</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, NoSQL, Tableau, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c267e74bf78cad0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cdc6ea1f306e70f</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Brook + Whittle</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Pinecone, Prompt Engineering, Docker, CI/CD, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ecf24f71ea50bb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Scientist - Machine Learning &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Battelle</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Crystal City, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, PostgreSQL, NoSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2022-12-08</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9454f5c5312fc674</t>
         </is>
       </c>
     </row>
